--- a/inputs_raw_cases/cases_202601.xlsx
+++ b/inputs_raw_cases/cases_202601.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ariellin1\Desktop\Case Complexity Index (CCI)\cases\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ariellin1\Desktop\Case Complexity Index (CCI)_V3\inputs_raw_cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A1DC8F0-3BE5-43B8-BC11-5D25BBA25D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC95BE25-622F-4199-9365-5EC317CB14F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{D3E80B60-251C-4A49-B4B0-80534DE0FEEB}"/>
   </bookViews>
@@ -38,19 +38,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>致伸</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>CAATS</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -69,19 +56,6 @@
   </si>
   <si>
     <t>否</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>星耀能源</t>
-    </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -372,6 +346,14 @@
       </rPr>
       <t>是否首查</t>
     </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>qq</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ww</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -379,7 +361,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -413,6 +395,12 @@
       <color theme="1"/>
       <name val="Microsoft JhengHei"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="4"/>
     </font>
   </fonts>
   <fills count="6">
@@ -476,7 +464,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -499,6 +487,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -837,63 +828,78 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E62AC8D5-96C7-46ED-93DF-478A08033A5F}">
   <dimension ref="A1:P3"/>
   <sheetFormatPr defaultRowHeight="17"/>
+  <cols>
+    <col min="1" max="2" width="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.90625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.26953125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:16" s="1" customFormat="1">
       <c r="A1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="M1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="N1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="P1" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="P1" s="6" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:16" s="1" customFormat="1">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -904,10 +910,10 @@
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
@@ -916,15 +922,15 @@
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
       <c r="P2" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:16" s="1" customFormat="1">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
+      <c r="A3" s="8" t="s">
+        <v>23</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -935,16 +941,16 @@
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L3" s="3"/>
       <c r="M3" s="4"/>
